--- a/경기철도-수원시-보고서.xlsx
+++ b/경기철도-수원시-보고서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 내 문서 모음\01. 업무관련 문서양식\017 지하안전점검(지하안전법) 관련\■ 연도별 지하안전점검(육안점검) 결과보고서\2026년 지하안전점검 보고서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E1B79B-0C33-4599-9298-3A92A4B5D13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD864D9D-8FD3-4012-ABCE-1B59E658AF07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-96" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="254">
   <si>
     <t>시행년도</t>
   </si>
@@ -670,9 +670,6 @@
   </si>
   <si>
     <t>26-수원시-23</t>
-  </si>
-  <si>
-    <t>긴급</t>
   </si>
   <si>
     <t>이의동421-5</t>
@@ -995,6 +992,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1002,12 +1005,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1367,14 +1364,14 @@
         <v>2026</v>
       </c>
       <c r="C2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B4" t="s">
@@ -1439,7 +1436,7 @@
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="17">
+      <c r="A5" s="11">
         <v>2026</v>
       </c>
       <c r="B5">
@@ -1504,7 +1501,7 @@
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="17">
+      <c r="A6" s="11">
         <v>2026</v>
       </c>
       <c r="B6">
@@ -1569,7 +1566,7 @@
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="17">
+      <c r="A7" s="11">
         <v>2026</v>
       </c>
       <c r="B7">
@@ -1634,7 +1631,7 @@
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="17">
+      <c r="A8" s="11">
         <v>2026</v>
       </c>
       <c r="B8">
@@ -1699,7 +1696,7 @@
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="17">
+      <c r="A9" s="11">
         <v>2026</v>
       </c>
       <c r="B9">
@@ -1764,7 +1761,7 @@
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="17">
+      <c r="A10" s="11">
         <v>2026</v>
       </c>
       <c r="B10">
@@ -1829,7 +1826,7 @@
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="17">
+      <c r="A11" s="11">
         <v>2026</v>
       </c>
       <c r="B11">
@@ -1894,7 +1891,7 @@
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="A12" s="11">
         <v>2026</v>
       </c>
       <c r="B12">
@@ -1959,7 +1956,7 @@
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
+      <c r="A13" s="11">
         <v>2026</v>
       </c>
       <c r="B13">
@@ -1975,7 +1972,7 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G13" t="s">
         <v>26</v>
@@ -2024,7 +2021,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
+      <c r="A14" s="11">
         <v>2026</v>
       </c>
       <c r="B14">
@@ -2089,7 +2086,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="17">
+      <c r="A15" s="11">
         <v>2026</v>
       </c>
       <c r="B15">
@@ -2154,7 +2151,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="17">
+      <c r="A16" s="11">
         <v>2026</v>
       </c>
       <c r="B16">
@@ -2219,7 +2216,7 @@
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A17" s="17">
+      <c r="A17" s="11">
         <v>2026</v>
       </c>
       <c r="B17">
@@ -2284,7 +2281,7 @@
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A18" s="17">
+      <c r="A18" s="11">
         <v>2026</v>
       </c>
       <c r="B18">
@@ -2294,7 +2291,7 @@
         <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E18" t="s">
         <v>26</v>
@@ -2342,14 +2339,14 @@
         <v>31</v>
       </c>
       <c r="T18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="U18" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A19" s="17">
+      <c r="A19" s="11">
         <v>2026</v>
       </c>
       <c r="B19">
@@ -2359,13 +2356,13 @@
         <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G19" t="s">
         <v>26</v>
@@ -2395,10 +2392,10 @@
         <v>4</v>
       </c>
       <c r="P19" t="s">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R19" t="s">
         <v>193</v>
@@ -2407,14 +2404,14 @@
         <v>31</v>
       </c>
       <c r="T19" t="s">
+        <v>220</v>
+      </c>
+      <c r="U19" t="s">
         <v>221</v>
       </c>
-      <c r="U19" t="s">
-        <v>222</v>
-      </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A20" s="17">
+      <c r="A20" s="11">
         <v>2026</v>
       </c>
       <c r="B20">
@@ -2479,7 +2476,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A21" s="17">
+      <c r="A21" s="11">
         <v>2026</v>
       </c>
       <c r="B21">
@@ -2544,7 +2541,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A22" s="17">
+      <c r="A22" s="11">
         <v>2026</v>
       </c>
       <c r="B22">
@@ -2609,7 +2606,7 @@
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A23" s="17">
+      <c r="A23" s="11">
         <v>2026</v>
       </c>
       <c r="B23">
@@ -2674,7 +2671,7 @@
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A24" s="17">
+      <c r="A24" s="11">
         <v>2026</v>
       </c>
       <c r="B24">
@@ -2739,7 +2736,7 @@
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A25" s="17">
+      <c r="A25" s="11">
         <v>2026</v>
       </c>
       <c r="B25">
@@ -2804,7 +2801,7 @@
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="17">
+      <c r="A26" s="11">
         <v>2026</v>
       </c>
       <c r="B26">
@@ -2869,7 +2866,7 @@
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A27" s="17">
+      <c r="A27" s="11">
         <v>2026</v>
       </c>
       <c r="B27">
@@ -2882,10 +2879,10 @@
         <v>209</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F27" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G27" t="s">
         <v>26</v>
@@ -2915,26 +2912,26 @@
         <v>4</v>
       </c>
       <c r="P27" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>241</v>
+      </c>
+      <c r="R27" t="s">
         <v>210</v>
       </c>
-      <c r="Q27" t="s">
-        <v>242</v>
-      </c>
-      <c r="R27" t="s">
+      <c r="S27" t="s">
+        <v>31</v>
+      </c>
+      <c r="T27" t="s">
         <v>211</v>
       </c>
-      <c r="S27" t="s">
-        <v>31</v>
-      </c>
-      <c r="T27" t="s">
-        <v>212</v>
-      </c>
       <c r="U27" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A28" s="17">
+      <c r="A28" s="11">
         <v>2026</v>
       </c>
       <c r="B28">
@@ -2944,7 +2941,7 @@
         <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E28" t="s">
         <v>26</v>
@@ -2986,20 +2983,20 @@
         <v>29</v>
       </c>
       <c r="R28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S28" t="s">
         <v>31</v>
       </c>
       <c r="T28" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U28" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="17">
+      <c r="A29" s="11">
         <v>2026</v>
       </c>
       <c r="B29">
@@ -3009,7 +3006,7 @@
         <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E29" t="s">
         <v>26</v>
@@ -3051,20 +3048,20 @@
         <v>29</v>
       </c>
       <c r="R29" t="s">
+        <v>215</v>
+      </c>
+      <c r="S29" t="s">
+        <v>31</v>
+      </c>
+      <c r="T29" t="s">
         <v>216</v>
       </c>
-      <c r="S29" t="s">
-        <v>31</v>
-      </c>
-      <c r="T29" t="s">
-        <v>217</v>
-      </c>
       <c r="U29" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A30" s="17">
+      <c r="A30" s="11">
         <v>2025</v>
       </c>
       <c r="B30">
@@ -3074,13 +3071,13 @@
         <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E30" t="s">
         <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G30" t="s">
         <v>28</v>
@@ -3113,20 +3110,20 @@
         <v>30</v>
       </c>
       <c r="R30" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="S30" t="s">
         <v>31</v>
       </c>
       <c r="T30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="U30" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A31" s="17">
+      <c r="A31" s="11">
         <v>2025</v>
       </c>
       <c r="B31">
@@ -3136,7 +3133,7 @@
         <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E31" t="s">
         <v>26</v>
@@ -3175,20 +3172,20 @@
         <v>30</v>
       </c>
       <c r="R31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S31" t="s">
         <v>31</v>
       </c>
       <c r="T31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A32" s="17">
+      <c r="A32" s="11">
         <v>2025</v>
       </c>
       <c r="B32">
@@ -3198,7 +3195,7 @@
         <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E32" t="s">
         <v>26</v>
@@ -3237,20 +3234,20 @@
         <v>30</v>
       </c>
       <c r="R32" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="S32" t="s">
         <v>31</v>
       </c>
       <c r="T32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U32" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A33" s="17">
+      <c r="A33" s="11">
         <v>2025</v>
       </c>
       <c r="B33">
@@ -3312,7 +3309,7 @@
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A34" s="17">
+      <c r="A34" s="11">
         <v>2025</v>
       </c>
       <c r="B34">
@@ -3374,7 +3371,7 @@
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A35" s="17">
+      <c r="A35" s="11">
         <v>2025</v>
       </c>
       <c r="B35">
@@ -3439,7 +3436,7 @@
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A36" s="17">
+      <c r="A36" s="11">
         <v>2025</v>
       </c>
       <c r="B36">
@@ -3501,7 +3498,7 @@
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A37" s="17">
+      <c r="A37" s="11">
         <v>2025</v>
       </c>
       <c r="B37">
@@ -3563,7 +3560,7 @@
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A38" s="17">
+      <c r="A38" s="11">
         <v>2025</v>
       </c>
       <c r="B38">
@@ -3625,7 +3622,7 @@
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A39" s="17">
+      <c r="A39" s="11">
         <v>2025</v>
       </c>
       <c r="B39">
@@ -3690,7 +3687,7 @@
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A40" s="17">
+      <c r="A40" s="11">
         <v>2025</v>
       </c>
       <c r="B40">
@@ -3752,7 +3749,7 @@
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A41" s="17">
+      <c r="A41" s="11">
         <v>2025</v>
       </c>
       <c r="B41">
@@ -3814,7 +3811,7 @@
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A42" s="17">
+      <c r="A42" s="11">
         <v>2025</v>
       </c>
       <c r="B42">
@@ -3879,7 +3876,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A43" s="17">
+      <c r="A43" s="11">
         <v>2025</v>
       </c>
       <c r="B43">
@@ -3941,7 +3938,7 @@
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A44" s="17">
+      <c r="A44" s="11">
         <v>2025</v>
       </c>
       <c r="B44">
@@ -4003,7 +4000,7 @@
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A45" s="17">
+      <c r="A45" s="11">
         <v>2025</v>
       </c>
       <c r="B45">
@@ -4065,7 +4062,7 @@
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A46" s="17">
+      <c r="A46" s="11">
         <v>2025</v>
       </c>
       <c r="B46">
@@ -4127,7 +4124,7 @@
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A47" s="17">
+      <c r="A47" s="11">
         <v>2025</v>
       </c>
       <c r="B47">
@@ -4189,7 +4186,7 @@
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A48" s="17">
+      <c r="A48" s="11">
         <v>2025</v>
       </c>
       <c r="B48">
@@ -4251,7 +4248,7 @@
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A49" s="17">
+      <c r="A49" s="11">
         <v>2025</v>
       </c>
       <c r="B49">
@@ -4316,7 +4313,7 @@
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A50" s="17">
+      <c r="A50" s="11">
         <v>2025</v>
       </c>
       <c r="B50">
@@ -4378,7 +4375,7 @@
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A51" s="17">
+      <c r="A51" s="11">
         <v>2025</v>
       </c>
       <c r="B51">
@@ -4440,7 +4437,7 @@
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A52" s="17">
+      <c r="A52" s="11">
         <v>2025</v>
       </c>
       <c r="B52">
@@ -4502,7 +4499,7 @@
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A53" s="17">
+      <c r="A53" s="11">
         <v>2025</v>
       </c>
       <c r="B53">
@@ -4564,7 +4561,7 @@
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A54" s="17">
+      <c r="A54" s="11">
         <v>2025</v>
       </c>
       <c r="B54">
@@ -4626,7 +4623,7 @@
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A55" s="17">
+      <c r="A55" s="11">
         <v>2025</v>
       </c>
       <c r="B55">
@@ -4691,7 +4688,7 @@
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A56" s="17">
+      <c r="A56" s="11">
         <v>2025</v>
       </c>
       <c r="B56">
@@ -4753,7 +4750,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A57" s="17">
+      <c r="A57" s="11">
         <v>2025</v>
       </c>
       <c r="B57">
@@ -4815,7 +4812,7 @@
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A58" s="17">
+      <c r="A58" s="11">
         <v>2025</v>
       </c>
       <c r="B58">
@@ -4877,7 +4874,7 @@
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A59" s="17">
+      <c r="A59" s="11">
         <v>2025</v>
       </c>
       <c r="B59">
@@ -4939,7 +4936,7 @@
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A60" s="17">
+      <c r="A60" s="11">
         <v>2025</v>
       </c>
       <c r="B60">
@@ -5004,7 +5001,7 @@
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A61" s="17">
+      <c r="A61" s="11">
         <v>2025</v>
       </c>
       <c r="B61">
@@ -5066,7 +5063,7 @@
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A62" s="17">
+      <c r="A62" s="11">
         <v>2025</v>
       </c>
       <c r="B62">
@@ -5131,7 +5128,7 @@
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A63" s="17">
+      <c r="A63" s="11">
         <v>2025</v>
       </c>
       <c r="B63">
@@ -5193,7 +5190,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A64" s="17">
+      <c r="A64" s="11">
         <v>2025</v>
       </c>
       <c r="B64">
@@ -5255,7 +5252,7 @@
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A65" s="17">
+      <c r="A65" s="11">
         <v>2025</v>
       </c>
       <c r="B65">
@@ -5320,7 +5317,7 @@
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A66" s="17">
+      <c r="A66" s="11">
         <v>2025</v>
       </c>
       <c r="B66">
@@ -5385,7 +5382,7 @@
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A67" s="17">
+      <c r="A67" s="11">
         <v>2025</v>
       </c>
       <c r="B67">
@@ -5450,7 +5447,7 @@
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A68" s="17">
+      <c r="A68" s="11">
         <v>2025</v>
       </c>
       <c r="B68">
@@ -5506,7 +5503,7 @@
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A69" s="17">
+      <c r="A69" s="11">
         <v>2025</v>
       </c>
       <c r="B69">
@@ -5565,7 +5562,7 @@
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A70" s="17">
+      <c r="A70" s="11">
         <v>2025</v>
       </c>
       <c r="B70">
@@ -5581,7 +5578,7 @@
         <v>26</v>
       </c>
       <c r="F70" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G70" t="s">
         <v>28</v>
@@ -5653,7 +5650,7 @@
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
@@ -5690,66 +5687,66 @@
       <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="16" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="16" t="s">
+      <c r="F4" s="14"/>
+      <c r="G4" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="16" t="s">
+      <c r="H4" s="13"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="16" t="s">
+      <c r="K4" s="13"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="K4" s="14"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="16" t="s">
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="14"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="15"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16" t="str">
+      <c r="B5" s="14"/>
+      <c r="C5" s="12" t="str">
         <f>RawData!D2</f>
         <v>수원시</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="16" t="s">
+      <c r="D5" s="14"/>
+      <c r="E5" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="F5" s="14"/>
+      <c r="G5" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="16" t="str">
+      <c r="H5" s="13"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="12" t="str">
         <f>RawData!C2</f>
         <v>경기철도㈜</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="15"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="14"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
@@ -5770,43 +5767,43 @@
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="13" t="s">
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="P7" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="P7" s="11" t="s">
-        <v>236</v>
-      </c>
     </row>
     <row r="8" spans="1:19" s="5" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
       <c r="D8" s="4" t="s">
         <v>7</v>
       </c>
@@ -5820,10 +5817,10 @@
         <v>10</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>8</v>
@@ -5832,14 +5829,14 @@
         <v>9</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -7532,6 +7529,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="N7:N8"/>
     <mergeCell ref="M5:P5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:D4"/>
@@ -7544,14 +7549,6 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:L5"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="N7:N8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
